--- a/Documents/VincentTranWeekLogs/TranVincentWeeklogs.xlsx
+++ b/Documents/VincentTranWeekLogs/TranVincentWeeklogs.xlsx
@@ -1,68 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/02b82688652a9224/Documents/CS356/VincentTranWeekLogs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF4220D6-FF60-43C8-AA63-93419FE39DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{2DB44B7A-CE96-43F3-880A-6AE81A090B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8B5AF4-E232-4919-B78F-7A06490DEC6F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="861" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="861" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="14" r:id="rId1"/>
     <sheet name="Jan 22-28" sheetId="1" r:id="rId2"/>
-    <sheet name="Jan 29-Feb 4" sheetId="2" r:id="rId3"/>
+    <sheet name="Jan 29-Feb 4" sheetId="16" r:id="rId3"/>
+    <sheet name="Feb 5-11" sheetId="17" r:id="rId4"/>
+    <sheet name="Feb 12-18" sheetId="19" r:id="rId5"/>
+    <sheet name="Feb 19-25" sheetId="20" r:id="rId6"/>
+    <sheet name="Feb 26- Mar 4" sheetId="21" r:id="rId7"/>
+    <sheet name="Mar 5- Mar 18" sheetId="2" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+  <si>
+    <t>Add a tab for the new week</t>
+  </si>
+  <si>
+    <t>Copy the template from the previsous sheet</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
   <si>
     <t>Date on which you worked on the project.</t>
   </si>
   <si>
+    <t>January 23, January 26, January 28</t>
+  </si>
+  <si>
     <t>Number of hours spent on that day.</t>
   </si>
   <si>
+    <t>1/2 hour, 1/2 hour, 1/2 hour</t>
+  </si>
+  <si>
     <t>Type of component, implementation or document.</t>
   </si>
   <si>
+    <t>Project Charter</t>
+  </si>
+  <si>
+    <t>Which specific part did you work with, e.g. requirement number or section of a document. (Mention multiple if necessary)</t>
+  </si>
+  <si>
+    <t>Section 2, Section 3.2, Section 3.5, Section 5</t>
+  </si>
+  <si>
     <t>Brief summary (3-4 sentences) of what was accomplished during this time.</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Established roles within the team with fellow team members 
+2.  Established in the Project Charter what the deliverables of the project were. 
+3. Wrote out the Risks, Constraints, and Assumptions for the project. 
+4. Signed the project charter document with teammates </t>
+  </si>
+  <si>
     <t>Total number of hours worked during the week.</t>
   </si>
   <si>
-    <t>Items</t>
-  </si>
-  <si>
-    <t>Update</t>
-  </si>
-  <si>
-    <t>1.
-2.
-3.
-4.</t>
-  </si>
-  <si>
-    <t>Which specific part did you work with, e.g. requirement number or section of a document. (Mention multiple if necessary)</t>
-  </si>
-  <si>
-    <t>Add a tab for the new week</t>
-  </si>
-  <si>
-    <t>Copy the template from the previsous sheet</t>
+    <t>1.5 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                       January 30th, Feburary 2nd</t>
+  </si>
+  <si>
+    <t>1/2 hour, 1/2 hour</t>
+  </si>
+  <si>
+    <t>SRS Document</t>
+  </si>
+  <si>
+    <t>Section 1.2, Section 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Coordinated with team who was responsible for each part of the SRS document. 
+2. Worked on submitting the scope of the submission/quiz section of the project.
+3. Helped contribute to making the user stories. </t>
+  </si>
+  <si>
+    <t>1 hour</t>
+  </si>
+  <si>
+    <t>Section 3.2, Section 3.3</t>
+  </si>
+  <si>
+    <t>1. Made 3 of the Functional Requirements
+2. Made 2 of the Use Cases                                                                                                                  3. Coordinated with team in collaboration of the previous 2 tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                       Feburary 6th, Feburary 9th, Febuary 11th</t>
+  </si>
+  <si>
+    <t>1/2 hour, 1 hour, 1/2 hour</t>
+  </si>
+  <si>
+    <t>2 hours</t>
+  </si>
+  <si>
+    <t>February 13th, February 16th</t>
+  </si>
+  <si>
+    <t>Section 3.4, Section 4.1</t>
+  </si>
+  <si>
+    <t>1. Wrote up the Non-Functional Requirements related to Availability and Security 
+2.  Discussed with team the desired Sequence Diagram formats                                                                                                                                                                      3. Made the Sequence Diagrams for Use Cases 2 and 3</t>
+  </si>
+  <si>
+    <t>Februrary 20th</t>
+  </si>
+  <si>
+    <t>1/2 hour</t>
+  </si>
+  <si>
+    <t>Section 1, Section 2, Section 3, Section 4</t>
+  </si>
+  <si>
+    <t>1. Went through the document with the group to make sure everything is correct
+2.  Helped delete lines not needed for final submission                                                                                                                                                                   3. Finalized SRS Doc Version 1</t>
+  </si>
+  <si>
+    <t>February 27th, March 2nd, March 4th</t>
+  </si>
+  <si>
+    <t>Design Document</t>
+  </si>
+  <si>
+    <t>Section 2.3, Section 3.1, Section 3.2</t>
+  </si>
+  <si>
+    <t>1. Collaborated with team on tasks for Design Document
+2. Filled out two lesson components (Test and Lesson)                                                                                                                                                  3. Started working on the User Interface Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>March 6th, March 16th, March 18th</t>
+  </si>
+  <si>
+    <t>Design Document, Sprint Planning Document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Finished the Design Document with team
+2. Discussed Roles for Sprint 1, and filled out Sprint 1 Document with Team                                                                                                                                           3. Began using PyCharm as the IDE for the project, and discussed documentation standard with team </t>
   </si>
 </sst>
 </file>
@@ -161,6 +277,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -171,13 +296,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -196,15 +321,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,16 +610,17 @@
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -514,7 +631,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="1" customFormat="1" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -529,7 +646,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="4"/>
       <c r="N1" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -544,180 +661,190 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
     </row>
     <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
     </row>
     <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="16"/>
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
     </row>
     <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
     </row>
     <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -743,13 +870,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0EE90E-D985-43C4-ACF1-0FBE2EB2A5A1}">
   <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -764,7 +891,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="4"/>
       <c r="N1" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -779,180 +906,922 @@
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="7"/>
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
     </row>
     <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="7"/>
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
     </row>
     <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961C2F1A-02C2-43A9-B49D-1DF04B81C4D5}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="7"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
     </row>
     <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DCACDF-8B19-459B-8F39-B5A4A2DF5E46}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5D69FB-B397-4ABA-A47A-52D52DEED914}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="16"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
     </row>
     <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
     </row>
     <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -974,4 +1843,749 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9396F50B-FC39-42E4-96EE-4AC8104AB88F}">
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:25" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="10"/>
+    </row>
+    <row r="4" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="162" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="19"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="P10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N7:Y7"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="N4:Y4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="N5:Y5"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="N6:Y6"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="N3:Y3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="16828060-15db-4724-b3dc-4e6cb1cf3e4e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004B5D3244059D9447AD692DC9248B7C56" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="08e38e5512e4ca9900323de6acb97aa2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="16828060-15db-4724-b3dc-4e6cb1cf3e4e" xmlns:ns4="bf1122ff-931b-4eef-9186-81b365bb0a0e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afdffb1ae8c8e15ac98914b4bf46da8d" ns3:_="" ns4:_="">
+    <xsd:import namespace="16828060-15db-4724-b3dc-4e6cb1cf3e4e"/>
+    <xsd:import namespace="bf1122ff-931b-4eef-9186-81b365bb0a0e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns4:MigrationSourceID" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="16828060-15db-4724-b3dc-4e6cb1cf3e4e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="14" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="15" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bf1122ff-931b-4eef-9186-81b365bb0a0e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationSourceID" ma:index="12" nillable="true" ma:displayName="MigrationSourceID" ma:internalName="MigrationSourceID" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB864A2-7E43-4C1F-A0A8-D78CC7F38545}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1325F4F5-01D6-4D0C-A2EB-9E3C2DC592A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="16828060-15db-4724-b3dc-4e6cb1cf3e4e"/>
+    <ds:schemaRef ds:uri="bf1122ff-931b-4eef-9186-81b365bb0a0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC81008-54EA-4CD7-90F8-8CB84982DAA1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="16828060-15db-4724-b3dc-4e6cb1cf3e4e"/>
+    <ds:schemaRef ds:uri="bf1122ff-931b-4eef-9186-81b365bb0a0e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>